--- a/sports_forms/006_personal_training_waiver--sports_forms.xlsx
+++ b/sports_forms/006_personal_training_waiver--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -983,12 +983,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'spouse_or_partner',_'value':_'spouse_or_partners'}</t>
+          <t>spouse_or_partner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Spouse or Partner', 'value': 'spouse_or_partners'}</t>
+          <t>Spouse or Partner</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'parent',_'value':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Parent', 'value': 'parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'male',_'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Male', 'value': 'male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'female',_'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Female', 'value': 'female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'decline',_'value':_'decline'}</t>
+          <t>decline</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Decline', 'value': 'decline'}</t>
+          <t>Decline</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'alabama',_'value':_'alabama'}</t>
+          <t>alabama</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Alabama', 'value': 'alabama'}</t>
+          <t>Alabama</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'alaska',_'value':_'alaska'}</t>
+          <t>alaska</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Alaska', 'value': 'alaska'}</t>
+          <t>Alaska</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'american_samoa',_'value':_'american_samoa'}</t>
+          <t>american_samoa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'American Samoa', 'value': 'american_samoa'}</t>
+          <t>American Samoa</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'arizona',_'value':_'arizona'}</t>
+          <t>arizona</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Arizona', 'value': 'arizona'}</t>
+          <t>Arizona</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'arkansas',_'value':_'arkansas'}</t>
+          <t>arkansas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Arkansas', 'value': 'arkansas'}</t>
+          <t>Arkansas</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'california',_'value':_'california'}</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'California', 'value': 'california'}</t>
+          <t>California</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'colorado',_'value':_'colorado'}</t>
+          <t>colorado</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Colorado', 'value': 'colorado'}</t>
+          <t>Colorado</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'connecticut',_'value':_'connecticut'}</t>
+          <t>connecticut</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Connecticut', 'value': 'connecticut'}</t>
+          <t>Connecticut</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'delaware',_'value':_'delaware'}</t>
+          <t>delaware</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Delaware', 'value': 'delaware'}</t>
+          <t>Delaware</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'district_of_columbia',_'value':_'district_of_columbia'}</t>
+          <t>district_of_columbia</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'District of Columbia', 'value': 'district_of_columbia'}</t>
+          <t>District of Columbia</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'florida',_'value':_'florida'}</t>
+          <t>florida</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Florida', 'value': 'florida'}</t>
+          <t>Florida</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'georgia',_'value':_'georgia'}</t>
+          <t>georgia</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Georgia', 'value': 'georgia'}</t>
+          <t>Georgia</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'guam',_'value':_'guam'}</t>
+          <t>guam</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Guam', 'value': 'guam'}</t>
+          <t>Guam</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'hawaii',_'value':_'hawaii'}</t>
+          <t>hawaii</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'Hawaii', 'value': 'hawaii'}</t>
+          <t>Hawaii</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'idaho',_'value':_'idaho'}</t>
+          <t>idaho</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Idaho', 'value': 'idaho'}</t>
+          <t>Idaho</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_'illinois',_'value':_'illinois'}</t>
+          <t>illinois</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': 'Illinois', 'value': 'illinois'}</t>
+          <t>Illinois</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_17,_'label':_'indiana',_'value':_'indiana'}</t>
+          <t>indiana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 17, 'label': 'Indiana', 'value': 'indiana'}</t>
+          <t>Indiana</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_18,_'label':_'iowa',_'value':_'iowa'}</t>
+          <t>iowa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 18, 'label': 'Iowa', 'value': 'iowa'}</t>
+          <t>Iowa</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_19,_'label':_'kansas',_'value':_'kansas'}</t>
+          <t>kansas</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 19, 'label': 'Kansas', 'value': 'kansas'}</t>
+          <t>Kansas</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'kentucky',_'value':_'kentucky'}</t>
+          <t>kentucky</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'Kentucky', 'value': 'kentucky'}</t>
+          <t>Kentucky</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'louisiana',_'value':_'louisiana'}</t>
+          <t>louisiana</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Louisiana', 'value': 'louisiana'}</t>
+          <t>Louisiana</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'maine',_'value':_'maine'}</t>
+          <t>maine</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'Maine', 'value': 'maine'}</t>
+          <t>Maine</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_'maryland',_'value':_'maryland'}</t>
+          <t>maryland</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 'Maryland', 'value': 'maryland'}</t>
+          <t>Maryland</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_'massachusetts',_'value':_'massachusetts'}</t>
+          <t>massachusetts</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 'Massachusetts', 'value': 'massachusetts'}</t>
+          <t>Massachusetts</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_25,_'label':_'michigan',_'value':_'michigan'}</t>
+          <t>michigan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 25, 'label': 'Michigan', 'value': 'michigan'}</t>
+          <t>Michigan</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_26,_'label':_'minnesota',_'value':_'minnesota'}</t>
+          <t>minnesota</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 26, 'label': 'Minnesota', 'value': 'minnesota'}</t>
+          <t>Minnesota</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_27,_'label':_'mississippi',_'value':_'mississippi'}</t>
+          <t>mississippi</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 27, 'label': 'Mississippi', 'value': 'mississippi'}</t>
+          <t>Mississippi</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_28,_'label':_'missouri',_'value':_'missouri'}</t>
+          <t>missouri</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 28, 'label': 'Missouri', 'value': 'missouri'}</t>
+          <t>Missouri</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_29,_'label':_'montana',_'value':_'montana'}</t>
+          <t>montana</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 29, 'label': 'Montana', 'value': 'montana'}</t>
+          <t>Montana</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_30,_'label':_'nebraska',_'value':_'nebraska'}</t>
+          <t>nebraska</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 30, 'label': 'Nebraska', 'value': 'nebraska'}</t>
+          <t>Nebraska</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_31,_'label':_'nevada',_'value':_'nevada'}</t>
+          <t>nevada</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 31, 'label': 'Nevada', 'value': 'nevada'}</t>
+          <t>Nevada</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_32,_'label':_'new_hampshire',_'value':_'new_hampshire'}</t>
+          <t>new_hampshire</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 32, 'label': 'New Hampshire', 'value': 'new_hampshire'}</t>
+          <t>New Hampshire</t>
         </is>
       </c>
     </row>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_33,_'label':_'new_jersey',_'value':_'new_jersey'}</t>
+          <t>new_jersey</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 33, 'label': 'New Jersey', 'value': 'new_jersey'}</t>
+          <t>New Jersey</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_34,_'label':_'new_mexico',_'value':_'new_mexico'}</t>
+          <t>new_mexico</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 34, 'label': 'New Mexico', 'value': 'new_mexico'}</t>
+          <t>New Mexico</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_35,_'label':_'new_york',_'value':_'new_york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 35, 'label': 'New York', 'value': 'new_york'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1764,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_36,_'label':_'north_carolina',_'value':_'north_carolina'}</t>
+          <t>north_carolina</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 36, 'label': 'North Carolina', 'value': 'north_carolina'}</t>
+          <t>North Carolina</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_37,_'label':_'north_dakota',_'value':_'north_dakota'}</t>
+          <t>north_dakota</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 37, 'label': 'North Dakota', 'value': 'north_dakota'}</t>
+          <t>North Dakota</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1798,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_38,_'label':_'ohio',_'value':_'ohio'}</t>
+          <t>ohio</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 38, 'label': 'Ohio', 'value': 'ohio'}</t>
+          <t>Ohio</t>
         </is>
       </c>
     </row>
@@ -1815,12 +1815,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_39,_'label':_'oklahoma',_'value':_'oklahoma'}</t>
+          <t>oklahoma</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 39, 'label': 'Oklahoma', 'value': 'oklahoma'}</t>
+          <t>Oklahoma</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_40,_'label':_'oregon',_'value':_'oregon'}</t>
+          <t>oregon</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 40, 'label': 'Oregon', 'value': 'oregon'}</t>
+          <t>Oregon</t>
         </is>
       </c>
     </row>
@@ -1849,12 +1849,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_41,_'label':_'pennsylvania',_'value':_'pennsylvania'}</t>
+          <t>pennsylvania</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 41, 'label': 'Pennsylvania', 'value': 'pennsylvania'}</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_42,_'label':_'puerto_rico',_'value':_'puerto_rico'}</t>
+          <t>puerto_rico</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 42, 'label': 'Puerto Rico', 'value': 'puerto_rico'}</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
     </row>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_43,_'label':_'rhode_island',_'value':_'rhode_island'}</t>
+          <t>rhode_island</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 43, 'label': 'Rhode Island', 'value': 'rhode_island'}</t>
+          <t>Rhode Island</t>
         </is>
       </c>
     </row>
@@ -1900,12 +1900,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_44,_'label':_'south_carolina',_'value':_'south_carolina'}</t>
+          <t>south_carolina</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 44, 'label': 'South Carolina', 'value': 'south_carolina'}</t>
+          <t>South Carolina</t>
         </is>
       </c>
     </row>
@@ -1917,12 +1917,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_45,_'label':_'south_dakota',_'value':_'south_dakota'}</t>
+          <t>south_dakota</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 45, 'label': 'South Dakota', 'value': 'south_dakota'}</t>
+          <t>South Dakota</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_46,_'label':_'tennessee',_'value':_'tennessee'}</t>
+          <t>tennessee</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 46, 'label': 'Tennessee', 'value': 'tennessee'}</t>
+          <t>Tennessee</t>
         </is>
       </c>
     </row>
@@ -1951,12 +1951,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_47,_'label':_'texas',_'value':_'texas'}</t>
+          <t>texas</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 47, 'label': 'Texas', 'value': 'texas'}</t>
+          <t>Texas</t>
         </is>
       </c>
     </row>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_48,_'label':_'utah',_'value':_'utah'}</t>
+          <t>utah</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 48, 'label': 'Utah', 'value': 'utah'}</t>
+          <t>Utah</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_49,_'label':_'vermont',_'value':_'vermont'}</t>
+          <t>vermont</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 49, 'label': 'Vermont', 'value': 'vermont'}</t>
+          <t>Vermont</t>
         </is>
       </c>
     </row>
@@ -2002,12 +2002,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_50,_'label':_'virgin_islands',_'value':_'virgin_islands'}</t>
+          <t>virgin_islands</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 50, 'label': 'Virgin Islands', 'value': 'virgin_islands'}</t>
+          <t>Virgin Islands</t>
         </is>
       </c>
     </row>
@@ -2019,12 +2019,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_51,_'label':_'virginia',_'value':_'virginia'}</t>
+          <t>virginia</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': 51, 'label': 'Virginia', 'value': 'virginia'}</t>
+          <t>Virginia</t>
         </is>
       </c>
     </row>
@@ -2036,12 +2036,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'id':_52,_'label':_'washington',_'value':_'washington'}</t>
+          <t>washington</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'id': 52, 'label': 'Washington', 'value': 'washington'}</t>
+          <t>Washington</t>
         </is>
       </c>
     </row>
@@ -2053,12 +2053,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'id':_53,_'label':_'west_virginia',_'value':_'west_virginia'}</t>
+          <t>west_virginia</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'id': 53, 'label': 'West Virginia', 'value': 'west_virginia'}</t>
+          <t>West Virginia</t>
         </is>
       </c>
     </row>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'id':_54,_'label':_'wisconsin',_'value':_'wisconsin'}</t>
+          <t>wisconsin</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'id': 54, 'label': 'Wisconsin', 'value': 'wisconsin'}</t>
+          <t>Wisconsin</t>
         </is>
       </c>
     </row>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'id':_55,_'label':_'wyoming',_'value':_'wyoming'}</t>
+          <t>wyoming</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'id': 55, 'label': 'Wyoming', 'value': 'wyoming'}</t>
+          <t>Wyoming</t>
         </is>
       </c>
     </row>
@@ -2104,63 +2104,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'id':_56,_'label':_'district_of_columbia',_'value':_'district_of_columbia'}</t>
+          <t>northern_mariana_islands</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'id': 56, 'label': 'District of Columbia', 'value': 'district_of_columbia'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>physical_address_state_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>{'id':_57,_'label':_'american_samoa',_'value':_'american_samoa'}</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>{'id': 57, 'label': 'American Samoa', 'value': 'american_samoa'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>physical_address_state_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>{'id':_58,_'label':_'guam',_'value':_'guam'}</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>{'id': 58, 'label': 'Guam', 'value': 'guam'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>physical_address_state_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>{'id':_59,_'label':_'northern_mariana_islands',_'value':_'northern_mariana_islands'}</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>{'id': 59, 'label': 'Northern Mariana Islands', 'value': 'northern_mariana_islands'}</t>
+          <t>Northern Mariana Islands</t>
         </is>
       </c>
     </row>
